--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/bio-bio.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/bio-bio.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>61270.68</v>
+        <v>61786.7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/bio-bio.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>554892-1-CM26</t>
+          <t>2421-2847-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,6 +569,67 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>35878.81</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554892-1-CM26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>72.232.500-1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>61786.7</v>
       </c>
     </row>
